--- a/rosnedra_forecast/2026/rosnedra_page3.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page3.xlsx
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -443,7 +443,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,13 @@
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>нефть (геол./извл.):
-D1 - 2,145/0,691 млн т
-D1(D3dm) - 184,337/5,530 млн т
+Dл - 0,109/0,043 млн.т.
+D1 - 2,241/0,713 млн.т
+D1(D3dm) - 172,442/5,173 млн.т
 газ (геол./извл.):
-D1 - 0,088/0,088 млрд м3
+D1 - 0,094/0,094 млрд.м3.
 конденсат (геол./извл.):
-D1 - 0,006/0,002 млн т</t>
+D1 - 0,006/0,003 млн.т</t>
         </is>
       </c>
     </row>
@@ -490,9 +491,13 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>нефть (извл./геол.):
-D1 - 0,864/2,701 млн т
+Dл - 0,389/0,119 млн.т
+D1 - 3,334/1,315 млн.т
+D1(D3dm) - 386,455/11,594 млн.т
 газ (извл./геол.):
-D1 - 0,041/0,041 млрд м3</t>
+D1 - 0,097/0,097 млрд.м3;
+конденсат (извл./геол.):
+D1 - 0,01/0,003 млн.т</t>
         </is>
       </c>
     </row>
@@ -513,11 +518,12 @@
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>нефть (извл./геол.):
-D1 - 1,532/4,785 млн т
+D1 - 1,78/0,614 млн.т
+D1(D3dm) - 151,245/4,537 млн.т.
 газ (извл./геол.):
-D1 - 0,072/0,072 млрд м3
+D1 - 0,076/0,076 млрд.м3;
 конденсат (извл./геол.):
-D1 - 0,004/0,001 млн т</t>
+D1 - 0,005/0,002 млн.т</t>
         </is>
       </c>
     </row>
@@ -538,8 +544,10 @@
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>нефть (геол./извл.):
-D1 - 0,974/0,314 млн т
-D1(D3dm) - 74,921/2,248 млн т</t>
+D1 - 2,439/0,748 млн.т,
+D1(D3dm)-245,679/7,340 млн.т
+газ (геол./извл.):
+D1 - 0,015/0,015 млрд. м3</t>
         </is>
       </c>
     </row>
@@ -554,15 +562,14 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Новоильинский</t>
+          <t>Бердышевский</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-D1 - 3,247 млн т
-газ (извл.):
-D1 - 0,154 млрд м3</t>
+D1 - 0,266 млн.т,
+D1(D3dm)-2,176 млн.т</t>
         </is>
       </c>
     </row>
@@ -577,15 +584,13 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Сурмогский</t>
+          <t>Новоильинский</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-D1 - 1,106 млн т
-газ (извл.):
-D1 - 0,053 млрд м3</t>
+D1 - 1,4 млн.т</t>
         </is>
       </c>
     </row>
@@ -600,15 +605,123 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
+          <t>Сурмогский</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,4 млн.т,
+D2 - 0,2 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Яйвинский</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,3 млн.т,
+D2 - 0,2 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>Центрально-Чекурский</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-D1 - 0,882 млн т
-газ (извл.):
-D1 - 0,042 млрд м3</t>
+D1 - 0,4 млн.т,
+D2 - 0,3 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Мельничный</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,3 млн.т,
+D2 - 0,2 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Восточно-Яринский</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,2 млн.т,
+D2 - 0,1 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Конюшорский</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D0 - 0,25 млн.т</t>
         </is>
       </c>
     </row>
